--- a/main/ig/ValueSet-MeltingPotVS.xlsx
+++ b/main/ig/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:13:35+00:00</t>
+    <t>2026-07-01T14:58:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-MeltingPotVS.xlsx
+++ b/main/ig/ValueSet-MeltingPotVS.xlsx
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:58:32+00:00</t>
+    <t>2026-07-03T07:33:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
